--- a/base_datas/crescimento_medio_receita_uf.xlsx
+++ b/base_datas/crescimento_medio_receita_uf.xlsx
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>352.8258985015473</v>
+        <v>346.3513209407099</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>518.3684480205009</v>
+        <v>518.9572811397998</v>
       </c>
     </row>
     <row r="4">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>370.2936554964252</v>
+        <v>372.4082935163486</v>
       </c>
     </row>
     <row r="7">
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>402.6280030220175</v>
+        <v>402.6501023737414</v>
       </c>
     </row>
     <row r="8">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>312.0432099511598</v>
+        <v>311.0953629472523</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>331.8499491667074</v>
+        <v>331.2844398061</v>
       </c>
     </row>
     <row r="11">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>508.1568039835303</v>
+        <v>507.162027823568</v>
       </c>
     </row>
     <row r="12">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>323.1941554943357</v>
+        <v>323.0078166100812</v>
       </c>
     </row>
     <row r="13">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>365.4276025590669</v>
+        <v>370.292841956347</v>
       </c>
     </row>
     <row r="15">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>460.1905992548718</v>
+        <v>466.4124326453836</v>
       </c>
     </row>
     <row r="16">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>373.4769569342349</v>
+        <v>373.8493634756269</v>
       </c>
     </row>
     <row r="17">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>586.1325603769413</v>
+        <v>584.6049473033295</v>
       </c>
     </row>
     <row r="19">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>314.1387770933393</v>
+        <v>315.1972757715734</v>
       </c>
     </row>
     <row r="20">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>278.744094945122</v>
+        <v>280.1277909159599</v>
       </c>
     </row>
     <row r="21">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>434.4008070131296</v>
+        <v>431.9701587728039</v>
       </c>
     </row>
     <row r="23">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>574.5377243814069</v>
+        <v>560.5221180726942</v>
       </c>
     </row>
     <row r="24">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>288.4352373823964</v>
+        <v>289.0576547849859</v>
       </c>
     </row>
     <row r="25">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>311.5186906083576</v>
+        <v>311.3808585532606</v>
       </c>
     </row>
     <row r="26">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>194.8915461529145</v>
+        <v>194.9212826451374</v>
       </c>
     </row>
     <row r="28">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>439.4367198199809</v>
+        <v>450.2502856008451</v>
       </c>
     </row>
   </sheetData>

--- a/base_datas/crescimento_medio_receita_uf.xlsx
+++ b/base_datas/crescimento_medio_receita_uf.xlsx
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>352.8258985015473</v>
+        <v>346.3513209407099</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>518.3684480205009</v>
+        <v>518.9572811397998</v>
       </c>
     </row>
     <row r="4">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>370.2936554964252</v>
+        <v>372.4082935163486</v>
       </c>
     </row>
     <row r="7">
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>402.6280030220175</v>
+        <v>402.6501023737414</v>
       </c>
     </row>
     <row r="8">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>312.0432099511598</v>
+        <v>311.0953629472523</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>331.8499491667074</v>
+        <v>331.2844398061</v>
       </c>
     </row>
     <row r="11">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>508.1568039835303</v>
+        <v>507.162027823568</v>
       </c>
     </row>
     <row r="12">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>323.1941554943357</v>
+        <v>323.0078166100812</v>
       </c>
     </row>
     <row r="13">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>365.4276025590669</v>
+        <v>370.292841956347</v>
       </c>
     </row>
     <row r="15">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>460.1905992548718</v>
+        <v>466.4124326453836</v>
       </c>
     </row>
     <row r="16">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>373.4769569342349</v>
+        <v>373.8493634756269</v>
       </c>
     </row>
     <row r="17">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>586.1325603769413</v>
+        <v>584.6049473033295</v>
       </c>
     </row>
     <row r="19">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>314.1387770933393</v>
+        <v>315.1972757715734</v>
       </c>
     </row>
     <row r="20">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>278.744094945122</v>
+        <v>280.1277909159599</v>
       </c>
     </row>
     <row r="21">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>434.4008070131296</v>
+        <v>431.9701587728039</v>
       </c>
     </row>
     <row r="23">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>574.5377243814069</v>
+        <v>560.5221180726942</v>
       </c>
     </row>
     <row r="24">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>311.5186906083576</v>
+        <v>311.3808585532606</v>
       </c>
     </row>
     <row r="26">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>194.8915461529145</v>
+        <v>194.9212826451374</v>
       </c>
     </row>
     <row r="28">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>439.4367198199809</v>
+        <v>450.2502856008451</v>
       </c>
     </row>
   </sheetData>
